--- a/output/yearly_benthic_cover_iteration_42_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_42_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.5383703986499</v>
+        <v>45.76023726592624</v>
       </c>
       <c r="M2" t="n">
-        <v>99.49652021570816</v>
+        <v>98.90310578552808</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.02600768413502</v>
+        <v>88.03641420980003</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94951051005663</v>
+        <v>45.93927040426286</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228711481203154</v>
+        <v>2.228745941650164</v>
       </c>
       <c r="E3" t="n">
-        <v>5.718084200574321</v>
+        <v>5.712863830891289</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742903827067718</v>
+        <v>0.7429153138833882</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98038450341656</v>
+        <v>33.97670927852115</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17357604511503</v>
+        <v>34.17410443863585</v>
       </c>
       <c r="I3" t="n">
-        <v>6.539198707585006</v>
+        <v>6.557854694447016</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643148919173237</v>
+        <v>4.643220711771176</v>
       </c>
       <c r="K3" t="n">
-        <v>11.97399231586498</v>
+        <v>11.96358579019996</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84177145878554</v>
+        <v>48.86175206987468</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7652742847071</v>
+        <v>106.7646082643375</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.02344562634273</v>
+        <v>87.04889098959642</v>
       </c>
       <c r="C4" t="n">
-        <v>42.57574399718961</v>
+        <v>42.5845242967489</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179968826346668</v>
+        <v>2.180804189534455</v>
       </c>
       <c r="E4" t="n">
-        <v>6.503149557677749</v>
+        <v>6.50269963204112</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444577368712971</v>
+        <v>0.7444732338177363</v>
       </c>
       <c r="G4" t="n">
-        <v>33.23722229165886</v>
+        <v>33.2458485090194</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24505589607967</v>
+        <v>34.24576875561586</v>
       </c>
       <c r="I4" t="n">
-        <v>5.460730462262891</v>
+        <v>5.476338958206973</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652860855445606</v>
+        <v>4.652957711360852</v>
       </c>
       <c r="K4" t="n">
-        <v>12.97655437365727</v>
+        <v>12.95110901040358</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2660572206091</v>
+        <v>44.28220406244621</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81835559145598</v>
+        <v>99.81783736959871</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.81436149883449</v>
+        <v>85.82499625819952</v>
       </c>
       <c r="C5" t="n">
-        <v>42.21414907147172</v>
+        <v>42.2105334661001</v>
       </c>
       <c r="D5" t="n">
-        <v>2.120842084339412</v>
+        <v>2.120906916548476</v>
       </c>
       <c r="E5" t="n">
-        <v>7.086544063162024</v>
+        <v>7.086051713008876</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457759834651337</v>
+        <v>0.7457951184797541</v>
       </c>
       <c r="G5" t="n">
-        <v>32.3357375347552</v>
+        <v>32.33272862721086</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30569523939616</v>
+        <v>34.30657545006868</v>
       </c>
       <c r="I5" t="n">
-        <v>4.558666697059458</v>
+        <v>4.571718942384405</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661099896657086</v>
+        <v>4.661219490498463</v>
       </c>
       <c r="K5" t="n">
-        <v>14.18563850116553</v>
+        <v>14.1750037418005</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44852547007768</v>
+        <v>43.46234226548253</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84831304271492</v>
+        <v>99.84787947338312</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.41065546769562</v>
+        <v>84.28027840168564</v>
       </c>
       <c r="C6" t="n">
-        <v>41.51834178695228</v>
+        <v>41.37572548295416</v>
       </c>
       <c r="D6" t="n">
-        <v>2.052259395090895</v>
+        <v>2.045119248667032</v>
       </c>
       <c r="E6" t="n">
-        <v>7.491482487695547</v>
+        <v>7.468760637502158</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468964488945483</v>
+        <v>0.7469205665968134</v>
       </c>
       <c r="G6" t="n">
-        <v>31.29008125730609</v>
+        <v>31.17736340124062</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35723664914923</v>
+        <v>34.3583460634534</v>
       </c>
       <c r="I6" t="n">
-        <v>3.80459642396839</v>
+        <v>3.815514942995526</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668102805590927</v>
+        <v>4.668253541230084</v>
       </c>
       <c r="K6" t="n">
-        <v>15.58934453230439</v>
+        <v>15.71972159831436</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76568405026946</v>
+        <v>42.77756072588748</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87337036952613</v>
+        <v>99.873007807156</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.73928566332127</v>
+        <v>82.46467857586651</v>
       </c>
       <c r="C7" t="n">
-        <v>40.43776595460837</v>
+        <v>40.15249665915911</v>
       </c>
       <c r="D7" t="n">
-        <v>1.970775616064726</v>
+        <v>1.956382623799929</v>
       </c>
       <c r="E7" t="n">
-        <v>7.723129465264688</v>
+        <v>7.675309723842261</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478516829623011</v>
+        <v>0.7478817707420775</v>
       </c>
       <c r="G7" t="n">
-        <v>30.04772657593393</v>
+        <v>29.82459436232788</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40117741626585</v>
+        <v>34.40256145413556</v>
       </c>
       <c r="I7" t="n">
-        <v>3.174551888315408</v>
+        <v>3.183687573880814</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674073018514381</v>
+        <v>4.674261067137985</v>
       </c>
       <c r="K7" t="n">
-        <v>17.26071433667871</v>
+        <v>17.53532142413348</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19583647471381</v>
+        <v>42.20619539051309</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8943167660009</v>
+        <v>99.89401347380567</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.7777065237067</v>
+        <v>87.27184528333737</v>
       </c>
       <c r="C8" t="n">
-        <v>42.820278987013</v>
+        <v>42.43910658093309</v>
       </c>
       <c r="D8" t="n">
-        <v>1.975045038980508</v>
+        <v>1.960553788805286</v>
       </c>
       <c r="E8" t="n">
-        <v>9.614021785932151</v>
+        <v>9.494927194596103</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494718040389058</v>
+        <v>0.7494763147910348</v>
       </c>
       <c r="G8" t="n">
-        <v>30.57450478993134</v>
+        <v>30.32463286916976</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47570298578967</v>
+        <v>34.4759104803876</v>
       </c>
       <c r="I8" t="n">
-        <v>5.704761343790969</v>
+        <v>5.582117668143622</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684198775243161</v>
+        <v>4.684226967443967</v>
       </c>
       <c r="K8" t="n">
-        <v>12.22229347629329</v>
+        <v>12.72815471666262</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76767988824488</v>
+        <v>44.64706398688393</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81025235155117</v>
+        <v>99.81432528447965</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.77448495290244</v>
+        <v>85.04104187028443</v>
       </c>
       <c r="C9" t="n">
-        <v>41.70214981249404</v>
+        <v>41.07408087488476</v>
       </c>
       <c r="D9" t="n">
-        <v>1.884691136683956</v>
+        <v>1.859262236041871</v>
       </c>
       <c r="E9" t="n">
-        <v>9.967996221501592</v>
+        <v>9.781084331149083</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508589917949351</v>
+        <v>0.750845361975308</v>
       </c>
       <c r="G9" t="n">
-        <v>29.17578943710025</v>
+        <v>28.75791780741648</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53951362256701</v>
+        <v>34.53888665086416</v>
       </c>
       <c r="I9" t="n">
-        <v>4.762766844536341</v>
+        <v>4.660261970491867</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692868698718344</v>
+        <v>4.692783512345675</v>
       </c>
       <c r="K9" t="n">
-        <v>14.22551504709758</v>
+        <v>14.95895812971555</v>
       </c>
       <c r="L9" t="n">
-        <v>43.9138695475253</v>
+        <v>43.81190217128459</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84153440711691</v>
+        <v>99.8449411758849</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.72781425530465</v>
+        <v>82.57983628250942</v>
       </c>
       <c r="C10" t="n">
-        <v>40.39416048455746</v>
+        <v>39.33516275582048</v>
       </c>
       <c r="D10" t="n">
-        <v>1.793508860626553</v>
+        <v>1.748730685582484</v>
       </c>
       <c r="E10" t="n">
-        <v>10.14828198864552</v>
+        <v>9.847882068734293</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752047308570961</v>
+        <v>0.752024231244775</v>
       </c>
       <c r="G10" t="n">
-        <v>27.76425051973311</v>
+        <v>27.04828417875509</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59417619426421</v>
+        <v>34.59311463725965</v>
       </c>
       <c r="I10" t="n">
-        <v>3.975253704895795</v>
+        <v>3.889649035653294</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700295678568507</v>
+        <v>4.700151445279843</v>
       </c>
       <c r="K10" t="n">
-        <v>16.27218574469534</v>
+        <v>17.42016371749058</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20135469173231</v>
+        <v>43.1152218052864</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8677009209851</v>
+        <v>99.87054827859745</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.60283791858598</v>
+        <v>79.95269045762407</v>
       </c>
       <c r="C11" t="n">
-        <v>38.88523091098189</v>
+        <v>37.31000437216092</v>
       </c>
       <c r="D11" t="n">
-        <v>1.699824553351993</v>
+        <v>1.632054511495866</v>
       </c>
       <c r="E11" t="n">
-        <v>10.17105107530799</v>
+        <v>9.731786589491874</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530663464500741</v>
+        <v>0.753041870749115</v>
       </c>
       <c r="G11" t="n">
-        <v>26.3139791360557</v>
+        <v>25.24360931394962</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64105193670341</v>
+        <v>34.63992605445929</v>
       </c>
       <c r="I11" t="n">
-        <v>3.317200205403841</v>
+        <v>3.245760425296357</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706664665312964</v>
+        <v>4.706511692181969</v>
       </c>
       <c r="K11" t="n">
-        <v>18.39716208141402</v>
+        <v>20.04730954237592</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60718329357921</v>
+        <v>42.53464027891724</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88957628597512</v>
+        <v>99.89195419345407</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.37944212471398</v>
+        <v>77.45017330572345</v>
       </c>
       <c r="C12" t="n">
-        <v>37.17524756804427</v>
+        <v>35.3087751928548</v>
       </c>
       <c r="D12" t="n">
-        <v>1.602709031286091</v>
+        <v>1.522257911156484</v>
       </c>
       <c r="E12" t="n">
-        <v>10.05120941325432</v>
+        <v>9.528405301717576</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539415293161243</v>
+        <v>0.7539195110321519</v>
       </c>
       <c r="G12" t="n">
-        <v>24.81059114440094</v>
+        <v>23.54534343897781</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68131034854172</v>
+        <v>34.68029750747899</v>
       </c>
       <c r="I12" t="n">
-        <v>2.767546099688996</v>
+        <v>2.707952691409506</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712134558225778</v>
+        <v>4.711996943950949</v>
       </c>
       <c r="K12" t="n">
-        <v>20.62055787528604</v>
+        <v>22.54982669427653</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11205010651957</v>
+        <v>42.05123810105489</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90785554984987</v>
+        <v>99.90983998818622</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.07495099917833</v>
+        <v>74.98942311005159</v>
       </c>
       <c r="C13" t="n">
-        <v>35.29834139545643</v>
+        <v>33.26528050768569</v>
       </c>
       <c r="D13" t="n">
-        <v>1.50291976192148</v>
+        <v>1.415402282817413</v>
       </c>
       <c r="E13" t="n">
-        <v>9.810157411094046</v>
+        <v>9.236036480331952</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546942782742699</v>
+        <v>0.7546765171616076</v>
       </c>
       <c r="G13" t="n">
-        <v>23.26581245127963</v>
+        <v>21.89256669911525</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71593680061642</v>
+        <v>34.71511978943395</v>
       </c>
       <c r="I13" t="n">
-        <v>2.308591056778307</v>
+        <v>2.258893108931375</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716839239214188</v>
+        <v>4.716728232260047</v>
       </c>
       <c r="K13" t="n">
-        <v>22.92504900082167</v>
+        <v>25.01057688994841</v>
       </c>
       <c r="L13" t="n">
-        <v>41.699733323175</v>
+        <v>41.64892169427119</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92312371945309</v>
+        <v>99.92477909190529</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.77228967994574</v>
+        <v>82.42753094457663</v>
       </c>
       <c r="C14" t="n">
-        <v>39.42524213809532</v>
+        <v>37.99982304809394</v>
       </c>
       <c r="D14" t="n">
-        <v>1.504727596842782</v>
+        <v>1.41699788724784</v>
       </c>
       <c r="E14" t="n">
-        <v>12.12216829944206</v>
+        <v>11.83197328234328</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556020863327835</v>
+        <v>0.7555272754293739</v>
       </c>
       <c r="G14" t="n">
-        <v>25.09016806414128</v>
+        <v>24.03816237912274</v>
       </c>
       <c r="H14" t="n">
-        <v>36.55406556037284</v>
+        <v>36.87517052774443</v>
       </c>
       <c r="I14" t="n">
-        <v>3.023045033234092</v>
+        <v>2.787654121255367</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722513039579898</v>
+        <v>4.722045471433588</v>
       </c>
       <c r="K14" t="n">
-        <v>16.22771032005427</v>
+        <v>17.57246905542338</v>
       </c>
       <c r="L14" t="n">
-        <v>44.24640044064841</v>
+        <v>44.33489072664216</v>
       </c>
       <c r="M14" t="n">
-        <v>99.899352898798</v>
+        <v>99.90718283015948</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.20304290859231</v>
+        <v>81.61861992366246</v>
       </c>
       <c r="C15" t="n">
-        <v>39.30277793159072</v>
+        <v>37.62092398673677</v>
       </c>
       <c r="D15" t="n">
-        <v>1.481708217128674</v>
+        <v>1.387573831715872</v>
       </c>
       <c r="E15" t="n">
-        <v>12.37754388819509</v>
+        <v>11.97382342877667</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563654554601837</v>
+        <v>0.7562447549599208</v>
       </c>
       <c r="G15" t="n">
-        <v>24.72686715277142</v>
+        <v>23.53900833584924</v>
       </c>
       <c r="H15" t="n">
-        <v>36.61152480426389</v>
+        <v>36.91018869439374</v>
       </c>
       <c r="I15" t="n">
-        <v>2.521749294146905</v>
+        <v>2.325251159467512</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72728409662615</v>
+        <v>4.726529718499505</v>
       </c>
       <c r="K15" t="n">
-        <v>16.7969570914077</v>
+        <v>18.38138007633754</v>
       </c>
       <c r="L15" t="n">
-        <v>43.81629150385619</v>
+        <v>43.92026110022416</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91602652685461</v>
+        <v>99.92256516329846</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.90276876763384</v>
+        <v>79.14579380620559</v>
       </c>
       <c r="C16" t="n">
-        <v>37.39245353011732</v>
+        <v>35.50677578377088</v>
       </c>
       <c r="D16" t="n">
-        <v>1.394585099385981</v>
+        <v>1.295644989656104</v>
       </c>
       <c r="E16" t="n">
-        <v>12.00030185313158</v>
+        <v>11.50375503827369</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570209119968668</v>
+        <v>0.756862424911667</v>
       </c>
       <c r="G16" t="n">
-        <v>23.2729494829798</v>
+        <v>21.97951382097076</v>
       </c>
       <c r="H16" t="n">
-        <v>36.64325187889118</v>
+        <v>36.9403354350095</v>
       </c>
       <c r="I16" t="n">
-        <v>2.103278841268021</v>
+        <v>1.939291941685948</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731380699980419</v>
+        <v>4.730390155697919</v>
       </c>
       <c r="K16" t="n">
-        <v>19.09723123236614</v>
+        <v>20.85420619379441</v>
       </c>
       <c r="L16" t="n">
-        <v>43.44026664601246</v>
+        <v>43.57442771244951</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92995140849592</v>
+        <v>99.93540969001479</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.76482018584768</v>
+        <v>81.02845210873153</v>
       </c>
       <c r="C17" t="n">
-        <v>38.73381941200887</v>
+        <v>36.8740170977</v>
       </c>
       <c r="D17" t="n">
-        <v>1.395769674807067</v>
+        <v>1.296663870232847</v>
       </c>
       <c r="E17" t="n">
-        <v>12.84128528971431</v>
+        <v>12.34174770932325</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576639336138294</v>
+        <v>0.7574576129687086</v>
       </c>
       <c r="G17" t="n">
-        <v>23.77200143219011</v>
+        <v>22.507145215478</v>
       </c>
       <c r="H17" t="n">
-        <v>37.1536607052097</v>
+        <v>37.47973185054979</v>
       </c>
       <c r="I17" t="n">
-        <v>2.10903956522622</v>
+        <v>1.911595769124506</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735399585086435</v>
+        <v>4.734110081054429</v>
       </c>
       <c r="K17" t="n">
-        <v>17.23517981415235</v>
+        <v>18.97154789126847</v>
       </c>
       <c r="L17" t="n">
-        <v>43.96075911900684</v>
+        <v>44.0907652212638</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92975834516805</v>
+        <v>99.93633021023227</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.44327157213816</v>
+        <v>78.68911422662111</v>
       </c>
       <c r="C18" t="n">
-        <v>36.73809387845281</v>
+        <v>34.82917593827078</v>
       </c>
       <c r="D18" t="n">
-        <v>1.31147280555213</v>
+        <v>1.213562795555051</v>
       </c>
       <c r="E18" t="n">
-        <v>12.35887739885432</v>
+        <v>11.81646390204046</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582161197708623</v>
+        <v>0.7579690950239019</v>
       </c>
       <c r="G18" t="n">
-        <v>22.3363023101738</v>
+        <v>21.06469895143612</v>
       </c>
       <c r="H18" t="n">
-        <v>37.18073832658553</v>
+        <v>37.50504047501509</v>
       </c>
       <c r="I18" t="n">
-        <v>1.758813862633647</v>
+        <v>1.594072163651088</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738850748567891</v>
+        <v>4.737306843899387</v>
       </c>
       <c r="K18" t="n">
-        <v>19.55672842786182</v>
+        <v>21.3108857733789</v>
       </c>
       <c r="L18" t="n">
-        <v>43.64659326131799</v>
+        <v>43.80683840587464</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94141556763262</v>
+        <v>99.94690011752432</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.54056437556028</v>
+        <v>77.80997879242219</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10644114091677</v>
+        <v>34.18209132697987</v>
       </c>
       <c r="D19" t="n">
-        <v>1.279379267571203</v>
+        <v>1.182418317038808</v>
       </c>
       <c r="E19" t="n">
-        <v>12.30086855959896</v>
+        <v>11.73681269554202</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586821226089016</v>
+        <v>0.7584047304168611</v>
       </c>
       <c r="G19" t="n">
-        <v>21.78970236276335</v>
+        <v>20.52410140976209</v>
       </c>
       <c r="H19" t="n">
-        <v>37.20358976581082</v>
+        <v>37.52659613361984</v>
       </c>
       <c r="I19" t="n">
-        <v>1.466579030901412</v>
+        <v>1.341615940937154</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741763266305636</v>
+        <v>4.740029565105382</v>
       </c>
       <c r="K19" t="n">
-        <v>20.45943562443972</v>
+        <v>22.19002120757783</v>
       </c>
       <c r="L19" t="n">
-        <v>43.38526729401479</v>
+        <v>43.58319262200592</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95114405937127</v>
+        <v>99.95530515656363</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.9896205932765</v>
+        <v>75.22388844232636</v>
       </c>
       <c r="C20" t="n">
-        <v>33.78138006232827</v>
+        <v>31.80198235001635</v>
       </c>
       <c r="D20" t="n">
-        <v>1.187736636167632</v>
+        <v>1.091525586189979</v>
       </c>
       <c r="E20" t="n">
-        <v>11.62355003808521</v>
+        <v>11.02102947950545</v>
       </c>
       <c r="F20" t="n">
-        <v>0.759083784385695</v>
+        <v>0.7587806424024023</v>
       </c>
       <c r="G20" t="n">
-        <v>20.22889415472108</v>
+        <v>18.94640965848458</v>
       </c>
       <c r="H20" t="n">
-        <v>37.22328610439995</v>
+        <v>37.54519662053326</v>
       </c>
       <c r="I20" t="n">
-        <v>1.222796223106329</v>
+        <v>1.118567440195656</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744273652410595</v>
+        <v>4.742379015015015</v>
       </c>
       <c r="K20" t="n">
-        <v>23.01037940672351</v>
+        <v>24.77611155767365</v>
       </c>
       <c r="L20" t="n">
-        <v>43.1675022245343</v>
+        <v>43.38463898283952</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95926169358609</v>
+        <v>99.96273289052951</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.71337660614513</v>
+        <v>81.33817387446732</v>
       </c>
       <c r="C21" t="n">
-        <v>37.30595669430421</v>
+        <v>35.69307299762966</v>
       </c>
       <c r="D21" t="n">
-        <v>1.188586991310316</v>
+        <v>1.092194556264104</v>
       </c>
       <c r="E21" t="n">
-        <v>13.53451896362072</v>
+        <v>13.09126095112425</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596272472882649</v>
+        <v>0.7592456810135121</v>
       </c>
       <c r="G21" t="n">
-        <v>21.84993253781251</v>
+        <v>20.77224724484843</v>
       </c>
       <c r="H21" t="n">
-        <v>38.85649155226917</v>
+        <v>39.38243296112703</v>
       </c>
       <c r="I21" t="n">
-        <v>1.776549018292482</v>
+        <v>1.495506973755532</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747670295551656</v>
+        <v>4.745285506334451</v>
       </c>
       <c r="K21" t="n">
-        <v>17.28662339385488</v>
+        <v>18.66182612553268</v>
       </c>
       <c r="L21" t="n">
-        <v>45.34824397799676</v>
+        <v>45.59528117768797</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94082406615586</v>
+        <v>99.95018030085032</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_42_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_42_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.76023726592624</v>
+        <v>45.53123106473696</v>
       </c>
       <c r="M2" t="n">
-        <v>98.90310578552808</v>
+        <v>98.87743296596653</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03641420980003</v>
+        <v>88.02024482511109</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93927040426286</v>
+        <v>45.87525595426899</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228745941650164</v>
+        <v>2.228753018314575</v>
       </c>
       <c r="E3" t="n">
-        <v>5.712863830891289</v>
+        <v>5.675639521561374</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429153138833882</v>
+        <v>0.742917672771525</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97670927852115</v>
+        <v>33.95461277653198</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17410443863585</v>
+        <v>34.17421294749014</v>
       </c>
       <c r="I3" t="n">
-        <v>6.557854694447016</v>
+        <v>6.600873433619466</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643220711771176</v>
+        <v>4.64323545482203</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96358579019996</v>
+        <v>11.97975517488891</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86175206987468</v>
+        <v>48.90805374597622</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7646082643375</v>
+        <v>106.7630648751341</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.04889098959642</v>
+        <v>87.19007413246821</v>
       </c>
       <c r="C4" t="n">
-        <v>42.5845242967489</v>
+        <v>42.68854027342814</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180804189534455</v>
+        <v>2.189154883322252</v>
       </c>
       <c r="E4" t="n">
-        <v>6.50269963204112</v>
+        <v>6.493520751563808</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444732338177363</v>
+        <v>0.7444832944093142</v>
       </c>
       <c r="G4" t="n">
-        <v>33.2458485090194</v>
+        <v>33.35134299774155</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24576875561586</v>
+        <v>34.24623154282844</v>
       </c>
       <c r="I4" t="n">
-        <v>5.476338958206973</v>
+        <v>5.512320072544626</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652957711360852</v>
+        <v>4.653020590058213</v>
       </c>
       <c r="K4" t="n">
-        <v>12.95110901040358</v>
+        <v>12.80992586753182</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28220406244621</v>
+        <v>44.31817626366173</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81783736959871</v>
+        <v>99.81664240462167</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.82499625819952</v>
+        <v>86.16831961252988</v>
       </c>
       <c r="C5" t="n">
-        <v>42.2105334661001</v>
+        <v>42.52234741717428</v>
       </c>
       <c r="D5" t="n">
-        <v>2.120906916548476</v>
+        <v>2.13974364124169</v>
       </c>
       <c r="E5" t="n">
-        <v>7.086051713008876</v>
+        <v>7.113918900545579</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457951184797541</v>
+        <v>0.7458085867303964</v>
       </c>
       <c r="G5" t="n">
-        <v>32.33272862721086</v>
+        <v>32.59857246737489</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30657545006868</v>
+        <v>34.30719498959822</v>
       </c>
       <c r="I5" t="n">
-        <v>4.571718942384405</v>
+        <v>4.601777359974153</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661219490498463</v>
+        <v>4.661303667064977</v>
       </c>
       <c r="K5" t="n">
-        <v>14.1750037418005</v>
+        <v>13.8316803874701</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46234226548253</v>
+        <v>43.4928521933405</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84787947338312</v>
+        <v>99.84687999798489</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.28027840168564</v>
+        <v>84.89179704516147</v>
       </c>
       <c r="C6" t="n">
-        <v>41.37572548295416</v>
+        <v>41.96065677296498</v>
       </c>
       <c r="D6" t="n">
-        <v>2.045119248667032</v>
+        <v>2.077608348305942</v>
       </c>
       <c r="E6" t="n">
-        <v>7.468760637502158</v>
+        <v>7.547439796583032</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469205665968134</v>
+        <v>0.7469332931991322</v>
       </c>
       <c r="G6" t="n">
-        <v>31.17736340124062</v>
+        <v>31.65195353111198</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3583460634534</v>
+        <v>34.35893148716006</v>
       </c>
       <c r="I6" t="n">
-        <v>3.815514942995526</v>
+        <v>3.840597506306746</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668253541230084</v>
+        <v>4.668333082494575</v>
       </c>
       <c r="K6" t="n">
-        <v>15.71972159831436</v>
+        <v>15.10820295483853</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77756072588748</v>
+        <v>42.80331312330833</v>
       </c>
       <c r="M6" t="n">
-        <v>99.873007807156</v>
+        <v>99.87217285111184</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.46467857586651</v>
+        <v>83.44647406423044</v>
       </c>
       <c r="C7" t="n">
-        <v>40.15249665915911</v>
+        <v>41.11202830858947</v>
       </c>
       <c r="D7" t="n">
-        <v>1.956382623799929</v>
+        <v>2.007426872516945</v>
       </c>
       <c r="E7" t="n">
-        <v>7.675309723842261</v>
+        <v>7.826586914369309</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478817707420775</v>
+        <v>0.7478894424885835</v>
       </c>
       <c r="G7" t="n">
-        <v>29.82459436232788</v>
+        <v>30.58275258559716</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40256145413556</v>
+        <v>34.40291435447482</v>
       </c>
       <c r="I7" t="n">
-        <v>3.183687573880814</v>
+        <v>3.204594879229988</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674261067137985</v>
+        <v>4.674309015553646</v>
       </c>
       <c r="K7" t="n">
-        <v>17.53532142413348</v>
+        <v>16.55352593576953</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20619539051309</v>
+        <v>42.22776249157693</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89401347380567</v>
+        <v>99.89331673593594</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.27184528333737</v>
+        <v>88.24234462634865</v>
       </c>
       <c r="C8" t="n">
-        <v>42.43910658093309</v>
+        <v>43.41321270024608</v>
       </c>
       <c r="D8" t="n">
-        <v>1.960553788805286</v>
+        <v>2.011656743467565</v>
       </c>
       <c r="E8" t="n">
-        <v>9.494927194596103</v>
+        <v>9.655168966692367</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494763147910348</v>
+        <v>0.7494653284500439</v>
       </c>
       <c r="G8" t="n">
-        <v>30.32463286916976</v>
+        <v>31.08839811330063</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4759104803876</v>
+        <v>34.475405108702</v>
       </c>
       <c r="I8" t="n">
-        <v>5.582117668143622</v>
+        <v>5.578092062923281</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684226967443967</v>
+        <v>4.684158302812774</v>
       </c>
       <c r="K8" t="n">
-        <v>12.72815471666262</v>
+        <v>11.75765537365135</v>
       </c>
       <c r="L8" t="n">
-        <v>44.64706398688393</v>
+        <v>44.64358648880983</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81432528447965</v>
+        <v>99.81445456270725</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.04104187028443</v>
+        <v>86.32611376236378</v>
       </c>
       <c r="C9" t="n">
-        <v>41.07408087488476</v>
+        <v>42.36319329666506</v>
       </c>
       <c r="D9" t="n">
-        <v>1.859262236041871</v>
+        <v>1.924952132139585</v>
       </c>
       <c r="E9" t="n">
-        <v>9.781084331149083</v>
+        <v>10.01514868117632</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750845361975308</v>
+        <v>0.7508129649034287</v>
       </c>
       <c r="G9" t="n">
-        <v>28.75791780741648</v>
+        <v>29.74845406768931</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53888665086416</v>
+        <v>34.53739638555771</v>
       </c>
       <c r="I9" t="n">
-        <v>4.660261970491867</v>
+        <v>4.65676850025099</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692783512345675</v>
+        <v>4.69258103064643</v>
       </c>
       <c r="K9" t="n">
-        <v>14.95895812971555</v>
+        <v>13.67388623763624</v>
       </c>
       <c r="L9" t="n">
-        <v>43.81190217128459</v>
+        <v>43.80797346395084</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8449411758849</v>
+        <v>99.84505299825214</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.57983628250942</v>
+        <v>84.02025413526655</v>
       </c>
       <c r="C10" t="n">
-        <v>39.33516275582048</v>
+        <v>40.78028162162406</v>
       </c>
       <c r="D10" t="n">
-        <v>1.748730685582484</v>
+        <v>1.821283983943267</v>
       </c>
       <c r="E10" t="n">
-        <v>9.847882068734293</v>
+        <v>10.12355431173054</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752024231244775</v>
+        <v>0.7519706729727017</v>
       </c>
       <c r="G10" t="n">
-        <v>27.04828417875509</v>
+        <v>28.14635337468519</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59311463725965</v>
+        <v>34.59065095674426</v>
       </c>
       <c r="I10" t="n">
-        <v>3.889649035653294</v>
+        <v>3.88662412911119</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700151445279843</v>
+        <v>4.699816706079386</v>
       </c>
       <c r="K10" t="n">
-        <v>17.42016371749058</v>
+        <v>15.97974586473346</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1152218052864</v>
+        <v>43.11061783307996</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87054827859745</v>
+        <v>99.87064531943749</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.95269045762407</v>
+        <v>81.66360583325572</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31000437216092</v>
+        <v>39.02632294814188</v>
       </c>
       <c r="D11" t="n">
-        <v>1.632054511495866</v>
+        <v>1.716494168851538</v>
       </c>
       <c r="E11" t="n">
-        <v>9.731786589491874</v>
+        <v>10.08160665284397</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753041870749115</v>
+        <v>0.7529661171793113</v>
       </c>
       <c r="G11" t="n">
-        <v>25.24360931394962</v>
+        <v>26.52691829940722</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63992605445929</v>
+        <v>34.6364413902483</v>
       </c>
       <c r="I11" t="n">
-        <v>3.245760425296357</v>
+        <v>3.243140972354687</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706511692181969</v>
+        <v>4.706038232370696</v>
       </c>
       <c r="K11" t="n">
-        <v>20.04730954237592</v>
+        <v>18.33639416674427</v>
       </c>
       <c r="L11" t="n">
-        <v>42.53464027891724</v>
+        <v>42.52932110374964</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89195419345407</v>
+        <v>99.8920382186358</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.45017330572345</v>
+        <v>79.22254765134339</v>
       </c>
       <c r="C12" t="n">
-        <v>35.3087751928548</v>
+        <v>37.08736330253006</v>
       </c>
       <c r="D12" t="n">
-        <v>1.522257911156484</v>
+        <v>1.608994141386602</v>
       </c>
       <c r="E12" t="n">
-        <v>9.528405301717576</v>
+        <v>9.901168174387353</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539195110321519</v>
+        <v>0.7538233209856501</v>
       </c>
       <c r="G12" t="n">
-        <v>23.54534343897781</v>
+        <v>24.86559925883376</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68029750747899</v>
+        <v>34.67587276533988</v>
       </c>
       <c r="I12" t="n">
-        <v>2.707952691409506</v>
+        <v>2.705694234249816</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711996943950949</v>
+        <v>4.711395756160313</v>
       </c>
       <c r="K12" t="n">
-        <v>22.54982669427653</v>
+        <v>20.77745234865662</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05123810105489</v>
+        <v>42.04509709958123</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90983998818622</v>
+        <v>99.90991275076792</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.98942311005159</v>
+        <v>76.76615499588425</v>
       </c>
       <c r="C13" t="n">
-        <v>33.26528050768569</v>
+        <v>35.04898310600228</v>
       </c>
       <c r="D13" t="n">
-        <v>1.415402282817413</v>
+        <v>1.50181188679558</v>
       </c>
       <c r="E13" t="n">
-        <v>9.236036480331952</v>
+        <v>9.617766479832984</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546765171616076</v>
+        <v>0.7545620776330817</v>
       </c>
       <c r="G13" t="n">
-        <v>21.89256669911525</v>
+        <v>23.20919112050339</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71511978943395</v>
+        <v>34.70985557112174</v>
       </c>
       <c r="I13" t="n">
-        <v>2.258893108931375</v>
+        <v>2.25695487479072</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716728232260047</v>
+        <v>4.716012985206762</v>
       </c>
       <c r="K13" t="n">
-        <v>25.01057688994841</v>
+        <v>23.23384500411574</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64892169427119</v>
+        <v>41.64201371670838</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92477909190529</v>
+        <v>99.92484182682639</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.42753094457663</v>
+        <v>83.61036021360727</v>
       </c>
       <c r="C14" t="n">
-        <v>37.99982304809394</v>
+        <v>39.30818350853842</v>
       </c>
       <c r="D14" t="n">
-        <v>1.41699788724784</v>
+        <v>1.503555837207292</v>
       </c>
       <c r="E14" t="n">
-        <v>11.83197328234328</v>
+        <v>11.98654125454608</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555272754293739</v>
+        <v>0.7554382984550908</v>
       </c>
       <c r="G14" t="n">
-        <v>24.03816237912274</v>
+        <v>25.10829399676262</v>
       </c>
       <c r="H14" t="n">
-        <v>36.87517052774443</v>
+        <v>36.62231337463914</v>
       </c>
       <c r="I14" t="n">
-        <v>2.787654121255367</v>
+        <v>2.912728086652729</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722045471433588</v>
+        <v>4.721489365344318</v>
       </c>
       <c r="K14" t="n">
-        <v>17.57246905542338</v>
+        <v>16.38963978639274</v>
       </c>
       <c r="L14" t="n">
-        <v>44.33489072664216</v>
+        <v>44.20519838307396</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90718283015948</v>
+        <v>99.90302167800512</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.61861992366246</v>
+        <v>82.7456662881378</v>
       </c>
       <c r="C15" t="n">
-        <v>37.62092398673677</v>
+        <v>38.89368102909228</v>
       </c>
       <c r="D15" t="n">
-        <v>1.387573831715872</v>
+        <v>1.47131133732384</v>
       </c>
       <c r="E15" t="n">
-        <v>11.97382342877667</v>
+        <v>12.13442545984133</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562447549599208</v>
+        <v>0.7561776926677481</v>
       </c>
       <c r="G15" t="n">
-        <v>23.53900833584924</v>
+        <v>24.56983419180049</v>
       </c>
       <c r="H15" t="n">
-        <v>36.91018869439374</v>
+        <v>36.65815789909429</v>
       </c>
       <c r="I15" t="n">
-        <v>2.325251159467512</v>
+        <v>2.42964912823667</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726529718499505</v>
+        <v>4.726110579173427</v>
       </c>
       <c r="K15" t="n">
-        <v>18.38138007633754</v>
+        <v>17.2543337118622</v>
       </c>
       <c r="L15" t="n">
-        <v>43.92026110022416</v>
+        <v>43.7710761455274</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92256516329846</v>
+        <v>99.91909088648188</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.14579380620559</v>
+        <v>80.24874808201872</v>
       </c>
       <c r="C16" t="n">
-        <v>35.50677578377088</v>
+        <v>36.77228174332497</v>
       </c>
       <c r="D16" t="n">
-        <v>1.295644989656104</v>
+        <v>1.376235918056817</v>
       </c>
       <c r="E16" t="n">
-        <v>11.50375503827369</v>
+        <v>11.68804012701791</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756862424911667</v>
+        <v>0.7568141833589439</v>
       </c>
       <c r="G16" t="n">
-        <v>21.97951382097076</v>
+        <v>22.98214351896467</v>
       </c>
       <c r="H16" t="n">
-        <v>36.9403354350095</v>
+        <v>36.68901384272421</v>
       </c>
       <c r="I16" t="n">
-        <v>1.939291941685948</v>
+        <v>2.026411845902755</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730390155697919</v>
+        <v>4.7300886459934</v>
       </c>
       <c r="K16" t="n">
-        <v>20.85420619379441</v>
+        <v>19.75125191798129</v>
       </c>
       <c r="L16" t="n">
-        <v>43.57442771244951</v>
+        <v>43.40897608513161</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93540969001479</v>
+        <v>99.93250974643786</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.02845210873153</v>
+        <v>81.84088760390394</v>
       </c>
       <c r="C17" t="n">
-        <v>36.8740170977</v>
+        <v>37.94102972521352</v>
       </c>
       <c r="D17" t="n">
-        <v>1.296663870232847</v>
+        <v>1.377364906039315</v>
       </c>
       <c r="E17" t="n">
-        <v>12.34174770932325</v>
+        <v>12.4348373983647</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574576129687086</v>
+        <v>0.7574350319407788</v>
       </c>
       <c r="G17" t="n">
-        <v>22.507145215478</v>
+        <v>23.40251711540821</v>
       </c>
       <c r="H17" t="n">
-        <v>37.47973185054979</v>
+        <v>37.12063179899743</v>
       </c>
       <c r="I17" t="n">
-        <v>1.911595769124506</v>
+        <v>2.014132403523639</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734110081054429</v>
+        <v>4.733968949629868</v>
       </c>
       <c r="K17" t="n">
-        <v>18.97154789126847</v>
+        <v>18.15911239609606</v>
       </c>
       <c r="L17" t="n">
-        <v>44.0907652212638</v>
+        <v>43.83277516286356</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93633021023227</v>
+        <v>99.93291728417314</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.68911422662111</v>
+        <v>79.50276708894678</v>
       </c>
       <c r="C18" t="n">
-        <v>34.82917593827078</v>
+        <v>35.91377454839635</v>
       </c>
       <c r="D18" t="n">
-        <v>1.213562795555051</v>
+        <v>1.291737069508174</v>
       </c>
       <c r="E18" t="n">
-        <v>11.81646390204046</v>
+        <v>11.94172770751546</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579690950239019</v>
+        <v>0.757968433634739</v>
       </c>
       <c r="G18" t="n">
-        <v>21.06469895143612</v>
+        <v>21.94763257378172</v>
       </c>
       <c r="H18" t="n">
-        <v>37.50504047501509</v>
+        <v>37.14677292932213</v>
       </c>
       <c r="I18" t="n">
-        <v>1.594072163651088</v>
+        <v>1.679625664967425</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737306843899387</v>
+        <v>4.737302710217119</v>
       </c>
       <c r="K18" t="n">
-        <v>21.3108857733789</v>
+        <v>20.49723291105322</v>
       </c>
       <c r="L18" t="n">
-        <v>43.80683840587464</v>
+        <v>43.53304441823033</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94690011752432</v>
+        <v>99.9440518776799</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.80997879242219</v>
+        <v>78.62605657157734</v>
       </c>
       <c r="C19" t="n">
-        <v>34.18209132697987</v>
+        <v>35.29563660942723</v>
       </c>
       <c r="D19" t="n">
-        <v>1.182418317038808</v>
+        <v>1.260294922965653</v>
       </c>
       <c r="E19" t="n">
-        <v>11.73681269554202</v>
+        <v>11.88447420122603</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584047304168611</v>
+        <v>0.7584184749763125</v>
       </c>
       <c r="G19" t="n">
-        <v>20.52410140976209</v>
+        <v>21.41340568199717</v>
       </c>
       <c r="H19" t="n">
-        <v>37.52659613361984</v>
+        <v>37.16882870734982</v>
       </c>
       <c r="I19" t="n">
-        <v>1.341615940937154</v>
+        <v>1.400519114460396</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740029565105382</v>
+        <v>4.740115468601954</v>
       </c>
       <c r="K19" t="n">
-        <v>22.19002120757783</v>
+        <v>21.37394342842267</v>
       </c>
       <c r="L19" t="n">
-        <v>43.58319262200592</v>
+        <v>43.28376369367878</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95530515656363</v>
+        <v>99.95334373152868</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.22388844232636</v>
+        <v>76.02505347385402</v>
       </c>
       <c r="C20" t="n">
-        <v>31.80198235001635</v>
+        <v>32.9101067271169</v>
       </c>
       <c r="D20" t="n">
-        <v>1.091525586189979</v>
+        <v>1.166036159911124</v>
       </c>
       <c r="E20" t="n">
-        <v>11.02102947950545</v>
+        <v>11.19023819450362</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587806424024023</v>
+        <v>0.7588067692643929</v>
       </c>
       <c r="G20" t="n">
-        <v>18.94640965848458</v>
+        <v>19.81187488504665</v>
       </c>
       <c r="H20" t="n">
-        <v>37.54519662053326</v>
+        <v>37.18785836493056</v>
       </c>
       <c r="I20" t="n">
-        <v>1.118567440195656</v>
+        <v>1.167696792295214</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742379015015015</v>
+        <v>4.742542307902457</v>
       </c>
       <c r="K20" t="n">
-        <v>24.77611155767365</v>
+        <v>23.974946526146</v>
       </c>
       <c r="L20" t="n">
-        <v>43.38463898283952</v>
+        <v>43.0760434380021</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96273289052951</v>
+        <v>99.961096691265</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.33817387446732</v>
+        <v>81.83112903172372</v>
       </c>
       <c r="C21" t="n">
-        <v>35.69307299762966</v>
+        <v>36.5051242559089</v>
       </c>
       <c r="D21" t="n">
-        <v>1.092194556264104</v>
+        <v>1.166839934018499</v>
       </c>
       <c r="E21" t="n">
-        <v>13.09126095112425</v>
+        <v>13.12928919387067</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592456810135121</v>
+        <v>0.7593298312882006</v>
       </c>
       <c r="G21" t="n">
-        <v>20.77224724484843</v>
+        <v>21.47482907352699</v>
       </c>
       <c r="H21" t="n">
-        <v>39.38243296112703</v>
+        <v>38.86279019706509</v>
       </c>
       <c r="I21" t="n">
-        <v>1.495506973755532</v>
+        <v>1.692239356403018</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745285506334451</v>
+        <v>4.745811445551254</v>
       </c>
       <c r="K21" t="n">
-        <v>18.66182612553268</v>
+        <v>18.16887096827628</v>
       </c>
       <c r="L21" t="n">
-        <v>45.59528117768797</v>
+        <v>45.26963565373095</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95018030085032</v>
+        <v>99.94363087791614</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_42_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_42_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.53123106473696</v>
+        <v>43.74102879966352</v>
       </c>
       <c r="M2" t="n">
-        <v>98.87743296596653</v>
+        <v>94.68327921517113</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.02024482511109</v>
+        <v>81.51724034194743</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87525595426899</v>
+        <v>43.27279589750299</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228753018314575</v>
+        <v>2.182639886109841</v>
       </c>
       <c r="E3" t="n">
-        <v>5.675639521561374</v>
+        <v>4.149998029894098</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742917672771525</v>
+        <v>0.7376614363838835</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95461277653198</v>
+        <v>32.83054162023551</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17421294749014</v>
+        <v>33.93242607365864</v>
       </c>
       <c r="I3" t="n">
-        <v>6.600873433619466</v>
+        <v>3.073589318266181</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64323545482203</v>
+        <v>4.610383977399271</v>
       </c>
       <c r="K3" t="n">
-        <v>11.97975517488891</v>
+        <v>18.48275965805257</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90805374597622</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7630648751341</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.19007413246821</v>
+        <v>88.64242461766695</v>
       </c>
       <c r="C4" t="n">
-        <v>42.68854027342814</v>
+        <v>42.85126914734769</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189154883322252</v>
+        <v>2.188412396550746</v>
       </c>
       <c r="E4" t="n">
-        <v>6.493520751563808</v>
+        <v>6.523854510335328</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444832944093142</v>
+        <v>0.7396123575461321</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35134299774155</v>
+        <v>33.51272025872933</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24623154282844</v>
+        <v>34.02216844712208</v>
       </c>
       <c r="I4" t="n">
-        <v>5.512320072544626</v>
+        <v>7.033079412720014</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653020590058213</v>
+        <v>4.622577234663326</v>
       </c>
       <c r="K4" t="n">
-        <v>12.80992586753182</v>
+        <v>11.35757538233304</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31817626366173</v>
+        <v>45.55733787614955</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81664240462167</v>
+        <v>99.76618240583028</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.16831961252988</v>
+        <v>87.64078432148953</v>
       </c>
       <c r="C5" t="n">
-        <v>42.52234741717428</v>
+        <v>42.93977581208413</v>
       </c>
       <c r="D5" t="n">
-        <v>2.13974364124169</v>
+        <v>2.141273149501743</v>
       </c>
       <c r="E5" t="n">
-        <v>7.113918900545579</v>
+        <v>7.362327075871763</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458085867303964</v>
+        <v>0.7412647382176347</v>
       </c>
       <c r="G5" t="n">
-        <v>32.59857246737489</v>
+        <v>32.79084333916411</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30719498959822</v>
+        <v>34.0981779580112</v>
       </c>
       <c r="I5" t="n">
-        <v>4.601777359974153</v>
+        <v>5.873993446862874</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661303667064977</v>
+        <v>4.632904613860218</v>
       </c>
       <c r="K5" t="n">
-        <v>13.8316803874701</v>
+        <v>12.35921567851046</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4928521933405</v>
+        <v>44.50564519238542</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84687999798489</v>
+        <v>99.80463668298</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.89179704516147</v>
+        <v>86.48858119607284</v>
       </c>
       <c r="C6" t="n">
-        <v>41.96065677296498</v>
+        <v>42.69933760051396</v>
       </c>
       <c r="D6" t="n">
-        <v>2.077608348305942</v>
+        <v>2.086876712730604</v>
       </c>
       <c r="E6" t="n">
-        <v>7.547439796583032</v>
+        <v>7.992670576850704</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469332931991322</v>
+        <v>0.7426658268996088</v>
       </c>
       <c r="G6" t="n">
-        <v>31.65195353111198</v>
+        <v>31.9578318960485</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35893148716006</v>
+        <v>34.16262803738201</v>
       </c>
       <c r="I6" t="n">
-        <v>3.840597506306746</v>
+        <v>4.904246728038859</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668333082494575</v>
+        <v>4.641661418122555</v>
       </c>
       <c r="K6" t="n">
-        <v>15.10820295483853</v>
+        <v>13.51141880392715</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80331312330833</v>
+        <v>43.62607711092382</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87217285111184</v>
+        <v>99.83683351536493</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.44647406423044</v>
+        <v>85.12637717101708</v>
       </c>
       <c r="C7" t="n">
-        <v>41.11202830858947</v>
+        <v>42.09898636636795</v>
       </c>
       <c r="D7" t="n">
-        <v>2.007426872516945</v>
+        <v>2.022488949845962</v>
       </c>
       <c r="E7" t="n">
-        <v>7.826586914369309</v>
+        <v>8.42830469312087</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478894424885835</v>
+        <v>0.7438562316874402</v>
       </c>
       <c r="G7" t="n">
-        <v>30.58275258559716</v>
+        <v>30.9718161482674</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40291435447482</v>
+        <v>34.21738665762225</v>
       </c>
       <c r="I7" t="n">
-        <v>3.204594879229988</v>
+        <v>4.093423042426654</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674309015553646</v>
+        <v>4.649101448046501</v>
       </c>
       <c r="K7" t="n">
-        <v>16.55352593576953</v>
+        <v>14.87362282898292</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22776249157693</v>
+        <v>42.89116172887027</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89331673593594</v>
+        <v>99.86377092422114</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.24234462634865</v>
+        <v>83.55792710119402</v>
       </c>
       <c r="C8" t="n">
-        <v>43.41321270024608</v>
+        <v>41.1665469312134</v>
       </c>
       <c r="D8" t="n">
-        <v>2.011656743467565</v>
+        <v>1.948559851736654</v>
       </c>
       <c r="E8" t="n">
-        <v>9.655168966692367</v>
+        <v>8.689526149494244</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494653284500439</v>
+        <v>0.7448698556541776</v>
       </c>
       <c r="G8" t="n">
-        <v>31.08839811330063</v>
+        <v>29.83968712732857</v>
       </c>
       <c r="H8" t="n">
-        <v>34.475405108702</v>
+        <v>34.26401336009217</v>
       </c>
       <c r="I8" t="n">
-        <v>5.578092062923281</v>
+        <v>3.415834159049578</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684158302812774</v>
+        <v>4.65543659783861</v>
       </c>
       <c r="K8" t="n">
-        <v>11.75765537365135</v>
+        <v>16.442072898806</v>
       </c>
       <c r="L8" t="n">
-        <v>44.64358648880983</v>
+        <v>42.27767397435763</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81445456270725</v>
+        <v>99.88629380437703</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.32611376236378</v>
+        <v>81.72744749342122</v>
       </c>
       <c r="C9" t="n">
-        <v>42.36319329666506</v>
+        <v>39.86658478741999</v>
       </c>
       <c r="D9" t="n">
-        <v>1.924952132139585</v>
+        <v>1.862604833866433</v>
       </c>
       <c r="E9" t="n">
-        <v>10.01514868117632</v>
+        <v>8.781185969277356</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508129649034287</v>
+        <v>0.7457356430165096</v>
       </c>
       <c r="G9" t="n">
-        <v>29.74845406768931</v>
+        <v>28.52339661770661</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53739638555771</v>
+        <v>34.30383957875944</v>
       </c>
       <c r="I9" t="n">
-        <v>4.65676850025099</v>
+        <v>2.84983708194169</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69258103064643</v>
+        <v>4.660847768853184</v>
       </c>
       <c r="K9" t="n">
-        <v>13.67388623763624</v>
+        <v>18.27255250657877</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80797346395084</v>
+        <v>41.76597842380543</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84505299825214</v>
+        <v>99.90511571780418</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.02025413526655</v>
+        <v>86.21497614288222</v>
       </c>
       <c r="C10" t="n">
-        <v>40.78028162162406</v>
+        <v>42.92727129392738</v>
       </c>
       <c r="D10" t="n">
-        <v>1.821283983943267</v>
+        <v>1.864741809804925</v>
       </c>
       <c r="E10" t="n">
-        <v>10.12355431173054</v>
+        <v>10.5474511663556</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519706729727017</v>
+        <v>0.7465912292882871</v>
       </c>
       <c r="G10" t="n">
-        <v>28.14635337468519</v>
+        <v>29.8177377637653</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59065095674426</v>
+        <v>35.60481265623858</v>
       </c>
       <c r="I10" t="n">
-        <v>3.88662412911119</v>
+        <v>2.967446334377726</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699816706079386</v>
+        <v>4.666195183051793</v>
       </c>
       <c r="K10" t="n">
-        <v>15.97974586473346</v>
+        <v>13.78502385711778</v>
       </c>
       <c r="L10" t="n">
-        <v>43.11061783307996</v>
+        <v>43.18890332662809</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87064531943749</v>
+        <v>99.90119847767326</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.66360583325572</v>
+        <v>85.95995735922708</v>
       </c>
       <c r="C11" t="n">
-        <v>39.02632294814188</v>
+        <v>43.05954210244611</v>
       </c>
       <c r="D11" t="n">
-        <v>1.716494168851538</v>
+        <v>1.848923921362677</v>
       </c>
       <c r="E11" t="n">
-        <v>10.08160665284397</v>
+        <v>10.90895823543232</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529661171793113</v>
+        <v>0.747319794234009</v>
       </c>
       <c r="G11" t="n">
-        <v>26.52691829940722</v>
+        <v>29.59636003019947</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6364413902483</v>
+        <v>35.67111247996695</v>
       </c>
       <c r="I11" t="n">
-        <v>3.243140972354687</v>
+        <v>2.516534184069082</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706038232370696</v>
+        <v>4.670748713962555</v>
       </c>
       <c r="K11" t="n">
-        <v>18.33639416674427</v>
+        <v>14.04004264077293</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52932110374964</v>
+        <v>42.81661256327426</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8920382186358</v>
+        <v>99.91619730649332</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.22254765134339</v>
+        <v>84.0944501890943</v>
       </c>
       <c r="C12" t="n">
-        <v>37.08736330253006</v>
+        <v>41.58557344777199</v>
       </c>
       <c r="D12" t="n">
-        <v>1.608994141386602</v>
+        <v>1.768957881853883</v>
       </c>
       <c r="E12" t="n">
-        <v>9.901168174387353</v>
+        <v>10.78695473691919</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538233209856501</v>
+        <v>0.7479415225423212</v>
       </c>
       <c r="G12" t="n">
-        <v>24.86559925883376</v>
+        <v>28.31631617974881</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67587276533988</v>
+        <v>35.70078885223609</v>
       </c>
       <c r="I12" t="n">
-        <v>2.705694234249816</v>
+        <v>2.098856499904517</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711395756160313</v>
+        <v>4.674634515889506</v>
       </c>
       <c r="K12" t="n">
-        <v>20.77745234865662</v>
+        <v>15.90554981090568</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04509709958123</v>
+        <v>42.43897301398707</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90991275076792</v>
+        <v>99.93009627266474</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.76615499588425</v>
+        <v>85.13686008398655</v>
       </c>
       <c r="C13" t="n">
-        <v>35.04898310600228</v>
+        <v>42.47603529064405</v>
       </c>
       <c r="D13" t="n">
-        <v>1.50181188679558</v>
+        <v>1.77031309983252</v>
       </c>
       <c r="E13" t="n">
-        <v>9.617766479832984</v>
+        <v>11.3865397683765</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545620776330817</v>
+        <v>0.7485145287222401</v>
       </c>
       <c r="G13" t="n">
-        <v>23.20919112050339</v>
+        <v>28.60320924886749</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70985557112174</v>
+        <v>35.99333924662587</v>
       </c>
       <c r="I13" t="n">
-        <v>2.25695487479072</v>
+        <v>1.95672838704793</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716012985206762</v>
+        <v>4.678215804513999</v>
       </c>
       <c r="K13" t="n">
-        <v>23.23384500411574</v>
+        <v>14.86313991601346</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64201371670838</v>
+        <v>42.59565044455557</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92484182682639</v>
+        <v>99.93482565121309</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.61036021360727</v>
+        <v>83.19692662039483</v>
       </c>
       <c r="C14" t="n">
-        <v>39.30818350853842</v>
+        <v>40.84041101374149</v>
       </c>
       <c r="D14" t="n">
-        <v>1.503555837207292</v>
+        <v>1.689178046576521</v>
       </c>
       <c r="E14" t="n">
-        <v>11.98654125454608</v>
+        <v>11.1366298315128</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554382984550908</v>
+        <v>0.7490038620754682</v>
       </c>
       <c r="G14" t="n">
-        <v>25.10829399676262</v>
+        <v>27.29229825469425</v>
       </c>
       <c r="H14" t="n">
-        <v>36.62231337463914</v>
+        <v>36.01686950650939</v>
       </c>
       <c r="I14" t="n">
-        <v>2.912728086652729</v>
+        <v>1.63167298105474</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721489365344318</v>
+        <v>4.681274137971675</v>
       </c>
       <c r="K14" t="n">
-        <v>16.38963978639274</v>
+        <v>16.80307337960516</v>
       </c>
       <c r="L14" t="n">
-        <v>44.20519838307396</v>
+        <v>42.30216204034647</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90302167800512</v>
+        <v>99.94564643369311</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.7456662881378</v>
+        <v>82.2815843308633</v>
       </c>
       <c r="C15" t="n">
-        <v>38.89368102909228</v>
+        <v>40.15799805287899</v>
       </c>
       <c r="D15" t="n">
-        <v>1.47131133732384</v>
+        <v>1.650562798075862</v>
       </c>
       <c r="E15" t="n">
-        <v>12.13442545984133</v>
+        <v>11.11208092129475</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561776926677481</v>
+        <v>0.7494226674337883</v>
       </c>
       <c r="G15" t="n">
-        <v>24.56983419180049</v>
+        <v>26.66838600258141</v>
       </c>
       <c r="H15" t="n">
-        <v>36.65815789909429</v>
+        <v>36.03700833182525</v>
       </c>
       <c r="I15" t="n">
-        <v>2.42964912823667</v>
+        <v>1.380231938191046</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726110579173427</v>
+        <v>4.683891671461176</v>
       </c>
       <c r="K15" t="n">
-        <v>17.2543337118622</v>
+        <v>17.71841566913671</v>
       </c>
       <c r="L15" t="n">
-        <v>43.7710761455274</v>
+        <v>42.07760425754871</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91909088648188</v>
+        <v>99.95401797956441</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.24874808201872</v>
+        <v>79.88889827850409</v>
       </c>
       <c r="C16" t="n">
-        <v>36.77228174332497</v>
+        <v>37.97946521733093</v>
       </c>
       <c r="D16" t="n">
-        <v>1.376235918056817</v>
+        <v>1.551150598376357</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68804012701791</v>
+        <v>10.63459927359234</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568141833589439</v>
+        <v>0.7497824983201742</v>
       </c>
       <c r="G16" t="n">
-        <v>22.98214351896467</v>
+        <v>25.06216846390751</v>
       </c>
       <c r="H16" t="n">
-        <v>36.68901384272421</v>
+        <v>36.0543112894408</v>
       </c>
       <c r="I16" t="n">
-        <v>2.026411845902755</v>
+        <v>1.150745540365812</v>
       </c>
       <c r="J16" t="n">
-        <v>4.7300886459934</v>
+        <v>4.686140614501087</v>
       </c>
       <c r="K16" t="n">
-        <v>19.75125191798129</v>
+        <v>20.11110172149591</v>
       </c>
       <c r="L16" t="n">
-        <v>43.40897608513161</v>
+        <v>41.87109328511229</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93250974643786</v>
+        <v>99.96166022393913</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.84088760390394</v>
+        <v>84.37507295287625</v>
       </c>
       <c r="C17" t="n">
-        <v>37.94102972521352</v>
+        <v>40.90835176419081</v>
       </c>
       <c r="D17" t="n">
-        <v>1.377364906039315</v>
+        <v>1.551970857168361</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4348373983647</v>
+        <v>12.20786322618192</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574350319407788</v>
+        <v>0.750178988310883</v>
       </c>
       <c r="G17" t="n">
-        <v>23.40251711540821</v>
+        <v>26.4199713020494</v>
       </c>
       <c r="H17" t="n">
-        <v>37.12063179899743</v>
+        <v>37.41792684609309</v>
       </c>
       <c r="I17" t="n">
-        <v>2.014132403523639</v>
+        <v>1.338543056129577</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733968949629868</v>
+        <v>4.688618676943017</v>
       </c>
       <c r="K17" t="n">
-        <v>18.15911239609606</v>
+        <v>15.62492704712377</v>
       </c>
       <c r="L17" t="n">
-        <v>43.83277516286356</v>
+        <v>43.42212666869431</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93291728417314</v>
+        <v>99.95540548000889</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.50276708894678</v>
+        <v>85.8068047173646</v>
       </c>
       <c r="C18" t="n">
-        <v>35.91377454839635</v>
+        <v>41.62611811718045</v>
       </c>
       <c r="D18" t="n">
-        <v>1.291737069508174</v>
+        <v>1.55318194935804</v>
       </c>
       <c r="E18" t="n">
-        <v>11.94172770751546</v>
+        <v>12.79344102344747</v>
       </c>
       <c r="F18" t="n">
-        <v>0.757968433634739</v>
+        <v>0.7507643961549852</v>
       </c>
       <c r="G18" t="n">
-        <v>21.94763257378172</v>
+        <v>26.5612140041429</v>
       </c>
       <c r="H18" t="n">
-        <v>37.14677292932213</v>
+        <v>37.44712620814809</v>
       </c>
       <c r="I18" t="n">
-        <v>1.679625664967425</v>
+        <v>2.008799660144441</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737302710217119</v>
+        <v>4.692277475968656</v>
       </c>
       <c r="K18" t="n">
-        <v>20.49723291105322</v>
+        <v>14.19319528263544</v>
       </c>
       <c r="L18" t="n">
-        <v>43.53304441823033</v>
+        <v>44.11377882350192</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9440518776799</v>
+        <v>99.9330922233178</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.62605657157734</v>
+        <v>83.07764427432885</v>
       </c>
       <c r="C19" t="n">
-        <v>35.29563660942723</v>
+        <v>39.20844088286554</v>
       </c>
       <c r="D19" t="n">
-        <v>1.260294922965653</v>
+        <v>1.45053590764574</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88447420122603</v>
+        <v>12.22714089408119</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584184749763125</v>
+        <v>0.7512689940301505</v>
       </c>
       <c r="G19" t="n">
-        <v>21.41340568199717</v>
+        <v>24.80584755675055</v>
       </c>
       <c r="H19" t="n">
-        <v>37.16882870734982</v>
+        <v>37.47229487679095</v>
       </c>
       <c r="I19" t="n">
-        <v>1.400519114460396</v>
+        <v>1.675124832341853</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740115468601954</v>
+        <v>4.695431212688439</v>
       </c>
       <c r="K19" t="n">
-        <v>21.37394342842267</v>
+        <v>16.92235572567114</v>
       </c>
       <c r="L19" t="n">
-        <v>43.28376369367878</v>
+        <v>43.81340340090379</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95334373152868</v>
+        <v>99.94420000944046</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.02505347385402</v>
+        <v>80.26735220101419</v>
       </c>
       <c r="C20" t="n">
-        <v>32.9101067271169</v>
+        <v>36.65715750590711</v>
       </c>
       <c r="D20" t="n">
-        <v>1.166036159911124</v>
+        <v>1.345389216691793</v>
       </c>
       <c r="E20" t="n">
-        <v>11.19023819450362</v>
+        <v>11.57360902401668</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588067692643929</v>
+        <v>0.7517047597261782</v>
       </c>
       <c r="G20" t="n">
-        <v>19.81187488504665</v>
+        <v>23.00771710499659</v>
       </c>
       <c r="H20" t="n">
-        <v>37.18785836493056</v>
+        <v>37.49403028819285</v>
       </c>
       <c r="I20" t="n">
-        <v>1.167696792295214</v>
+        <v>1.396747059101479</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742542307902457</v>
+        <v>4.698154748288613</v>
       </c>
       <c r="K20" t="n">
-        <v>23.974946526146</v>
+        <v>19.73264779898581</v>
       </c>
       <c r="L20" t="n">
-        <v>43.0760434380021</v>
+        <v>43.56366344976426</v>
       </c>
       <c r="M20" t="n">
-        <v>99.961096691265</v>
+        <v>99.95346875465718</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.83112903172372</v>
+        <v>77.50605915561849</v>
       </c>
       <c r="C21" t="n">
-        <v>36.5051242559089</v>
+        <v>34.11111970713296</v>
       </c>
       <c r="D21" t="n">
-        <v>1.166839934018499</v>
+        <v>1.242605918251094</v>
       </c>
       <c r="E21" t="n">
-        <v>13.12928919387067</v>
+        <v>10.88351327562635</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593298312882006</v>
+        <v>0.7520812418555224</v>
       </c>
       <c r="G21" t="n">
-        <v>21.47482907352699</v>
+        <v>21.25000340824426</v>
       </c>
       <c r="H21" t="n">
-        <v>38.86279019706509</v>
+        <v>37.51280871440068</v>
       </c>
       <c r="I21" t="n">
-        <v>1.692239356403018</v>
+        <v>1.164538835643554</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745811445551254</v>
+        <v>4.700507761597014</v>
       </c>
       <c r="K21" t="n">
-        <v>18.16887096827628</v>
+        <v>22.49394084438152</v>
       </c>
       <c r="L21" t="n">
-        <v>45.26963565373095</v>
+        <v>43.35614091906604</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94363087791614</v>
+        <v>99.96120147058051</v>
       </c>
     </row>
   </sheetData>
